--- a/test/fixtures/files/Sara-Alert-Format-With-Jurisdictions-EW.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-With-Jurisdictions-EW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885F5B4B-1CAB-9C48-A559-DD04507159F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FBCDAF-46DB-6347-84A7-535A3BFD7254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="20540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monitorees" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="430">
   <si>
     <t>First Name</t>
   </si>
@@ -1295,6 +1295,21 @@
   </si>
   <si>
     <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>Follow-Up Reason</t>
+  </si>
+  <si>
+    <t>Follow-Up Note</t>
+  </si>
+  <si>
+    <t>Needs Interpretation</t>
+  </si>
+  <si>
+    <t>note 1</t>
+  </si>
+  <si>
+    <t>note 2</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DH12"/>
+  <dimension ref="A1:DJ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1762,9 +1777,11 @@
     <col min="110" max="110" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="111" max="111" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2101,8 +2118,14 @@
       <c r="DH1" t="s">
         <v>411</v>
       </c>
+      <c r="DI1" t="s">
+        <v>425</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>426</v>
+      </c>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -2415,8 +2438,14 @@
       <c r="DH2" t="s">
         <v>417</v>
       </c>
+      <c r="DI2" t="s">
+        <v>427</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>428</v>
+      </c>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -2723,8 +2752,11 @@
       <c r="DG3">
         <v>2</v>
       </c>
+      <c r="DJ3" t="s">
+        <v>429</v>
+      </c>
     </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -3026,7 +3058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -3271,7 +3303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -3534,7 +3566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>201</v>
       </c>
@@ -3803,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>220</v>
       </c>
@@ -4063,7 +4095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -4342,7 +4374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>255</v>
       </c>
@@ -4620,7 +4652,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="11" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>275</v>
       </c>
@@ -4874,7 +4906,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>297</v>
       </c>

--- a/test/fixtures/files/Sara-Alert-Format-With-Jurisdictions-EW.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-With-Jurisdictions-EW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FBCDAF-46DB-6347-84A7-535A3BFD7254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E93576D-C457-F644-8776-B40E87D736BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="20540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="431">
   <si>
     <t>First Name</t>
   </si>
@@ -1310,6 +1310,9 @@
   </si>
   <si>
     <t>note 2</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -2752,6 +2755,9 @@
       <c r="DG3">
         <v>2</v>
       </c>
+      <c r="DI3" t="s">
+        <v>430</v>
+      </c>
       <c r="DJ3" t="s">
         <v>429</v>
       </c>

--- a/test/fixtures/files/Sara-Alert-Format-With-Jurisdictions-EW.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-With-Jurisdictions-EW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885F5B4B-1CAB-9C48-A559-DD04507159F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E93576D-C457-F644-8776-B40E87D736BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="20540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monitorees" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="431">
   <si>
     <t>First Name</t>
   </si>
@@ -1295,6 +1295,24 @@
   </si>
   <si>
     <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>Follow-Up Reason</t>
+  </si>
+  <si>
+    <t>Follow-Up Note</t>
+  </si>
+  <si>
+    <t>Needs Interpretation</t>
+  </si>
+  <si>
+    <t>note 1</t>
+  </si>
+  <si>
+    <t>note 2</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DH12"/>
+  <dimension ref="A1:DJ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1762,9 +1780,11 @@
     <col min="110" max="110" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="111" max="111" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2101,8 +2121,14 @@
       <c r="DH1" t="s">
         <v>411</v>
       </c>
+      <c r="DI1" t="s">
+        <v>425</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>426</v>
+      </c>
     </row>
-    <row r="2" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -2415,8 +2441,14 @@
       <c r="DH2" t="s">
         <v>417</v>
       </c>
+      <c r="DI2" t="s">
+        <v>427</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>428</v>
+      </c>
     </row>
-    <row r="3" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -2723,8 +2755,14 @@
       <c r="DG3">
         <v>2</v>
       </c>
+      <c r="DI3" t="s">
+        <v>430</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>429</v>
+      </c>
     </row>
-    <row r="4" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -3026,7 +3064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>167</v>
       </c>
@@ -3271,7 +3309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>180</v>
       </c>
@@ -3534,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>201</v>
       </c>
@@ -3803,7 +3841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>220</v>
       </c>
@@ -4063,7 +4101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>239</v>
       </c>
@@ -4342,7 +4380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>255</v>
       </c>
@@ -4620,7 +4658,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="11" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>275</v>
       </c>
@@ -4874,7 +4912,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:112" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:114" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>297</v>
       </c>
